--- a/input/input.xlsx
+++ b/input/input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manan.anand\OneDrive - ION\Desktop\linkedin_mapper\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iontradingcom-my.sharepoint.com/personal/manan_anand_iongroup_com/Documents/Desktop/linkedin_mapper/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E382995-B41D-44AA-A03B-D9E5F7835DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{8E382995-B41D-44AA-A03B-D9E5F7835DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E2F9F8-1EFC-4F2D-ACEC-43AB72AA6D89}"/>
   <bookViews>
-    <workbookView xWindow="-14610" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14190" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -33,10 +33,22 @@
     <t>Company</t>
   </si>
   <si>
-    <t>BRED BANQUE POPULAIRE</t>
-  </si>
-  <si>
-    <t>Fabrice MIQUEL</t>
+    <t>SOCIETE GENERALE PRIVATE BANKING</t>
+  </si>
+  <si>
+    <t>Valentin PILLET</t>
+  </si>
+  <si>
+    <t>SOCIETE GENERALE PRIVATE BANKING (LUXEMBOURG)</t>
+  </si>
+  <si>
+    <t>Mathieu PERFETTI</t>
+  </si>
+  <si>
+    <t>SOCIETE GENERALE SECURITIES SERVICES</t>
+  </si>
+  <si>
+    <t>Ruben BOTBOL</t>
   </si>
 </sst>
 </file>
@@ -53,13 +65,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +72,13 @@
     </font>
     <font>
       <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,12 +120,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -397,36 +412,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
+    </row>
+    <row r="8" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="C10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
